--- a/data/nzd0542/nzd0542.xlsx
+++ b/data/nzd0542/nzd0542.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J533"/>
+  <dimension ref="A1:J535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19615,9 +19615,81 @@
         <v>275.16</v>
       </c>
       <c r="I533" t="n">
-        <v>286.64</v>
+        <v>290.91</v>
       </c>
       <c r="J533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>283.48</v>
+      </c>
+      <c r="C534" t="n">
+        <v>271.11</v>
+      </c>
+      <c r="D534" t="n">
+        <v>268.33</v>
+      </c>
+      <c r="E534" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="F534" t="n">
+        <v>270.77</v>
+      </c>
+      <c r="G534" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="H534" t="n">
+        <v>280.67</v>
+      </c>
+      <c r="I534" t="n">
+        <v>296.24</v>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:15:17+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>285.25</v>
+      </c>
+      <c r="C535" t="n">
+        <v>272.15</v>
+      </c>
+      <c r="D535" t="n">
+        <v>268.84</v>
+      </c>
+      <c r="E535" t="n">
+        <v>265.05</v>
+      </c>
+      <c r="F535" t="n">
+        <v>270.53</v>
+      </c>
+      <c r="G535" t="n">
+        <v>271.33</v>
+      </c>
+      <c r="H535" t="n">
+        <v>281.36</v>
+      </c>
+      <c r="I535" t="n">
+        <v>296.64</v>
+      </c>
+      <c r="J535" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19634,7 +19706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B556"/>
+  <dimension ref="A1:B558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25197,6 +25269,26 @@
       </c>
       <c r="B556" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -25365,28 +25457,28 @@
         <v>0.0309</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3401633181538458</v>
+        <v>-0.348556794867436</v>
       </c>
       <c r="J2" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K2" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03517828828371417</v>
+        <v>0.03707641095883074</v>
       </c>
       <c r="M2" t="n">
-        <v>10.08804653248409</v>
+        <v>10.0905208739015</v>
       </c>
       <c r="N2" t="n">
-        <v>165.0640831843474</v>
+        <v>164.8825482838907</v>
       </c>
       <c r="O2" t="n">
-        <v>12.84772677108085</v>
+        <v>12.84065996294157</v>
       </c>
       <c r="P2" t="n">
-        <v>304.1245349417596</v>
+        <v>304.2135419393366</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25443,28 +25535,28 @@
         <v>0.0262</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3920548151370016</v>
+        <v>-0.4016314652907365</v>
       </c>
       <c r="J3" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K3" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06040052101666216</v>
+        <v>0.06342663695689954</v>
       </c>
       <c r="M3" t="n">
-        <v>8.649035580602172</v>
+        <v>8.660121871408121</v>
       </c>
       <c r="N3" t="n">
-        <v>124.7798930647983</v>
+        <v>124.879687358739</v>
       </c>
       <c r="O3" t="n">
-        <v>11.170492069054</v>
+        <v>11.17495804729213</v>
       </c>
       <c r="P3" t="n">
-        <v>294.2805314151519</v>
+        <v>294.3819822107868</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25521,28 +25613,28 @@
         <v>0.0305</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.379540419229619</v>
+        <v>-0.3870617495774789</v>
       </c>
       <c r="J4" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K4" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09081330268168586</v>
+        <v>0.09442400099772408</v>
       </c>
       <c r="M4" t="n">
-        <v>6.767452954532475</v>
+        <v>6.77865936419533</v>
       </c>
       <c r="N4" t="n">
-        <v>75.51219632711688</v>
+        <v>75.58229429331739</v>
       </c>
       <c r="O4" t="n">
-        <v>8.689775389911807</v>
+        <v>8.693807813226456</v>
       </c>
       <c r="P4" t="n">
-        <v>288.3083211624572</v>
+        <v>288.3877177281695</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25599,28 +25691,28 @@
         <v>0.0369</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4037848749514165</v>
+        <v>-0.4083951415506673</v>
       </c>
       <c r="J5" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K5" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1229142893460489</v>
+        <v>0.1260665315194118</v>
       </c>
       <c r="M5" t="n">
-        <v>6.308574765315263</v>
+        <v>6.306069821373166</v>
       </c>
       <c r="N5" t="n">
-        <v>60.91681507564521</v>
+        <v>60.82144812226591</v>
       </c>
       <c r="O5" t="n">
-        <v>7.80492249004724</v>
+        <v>7.798810686397376</v>
       </c>
       <c r="P5" t="n">
-        <v>281.3505636184939</v>
+        <v>281.3992303972591</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25677,28 +25769,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4581584249980062</v>
+        <v>-0.4576358245418586</v>
       </c>
       <c r="J6" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K6" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1718025973589643</v>
+        <v>0.1726703996409675</v>
       </c>
       <c r="M6" t="n">
-        <v>5.812004246297026</v>
+        <v>5.792518374648097</v>
       </c>
       <c r="N6" t="n">
-        <v>52.98255857562829</v>
+        <v>52.78587836923987</v>
       </c>
       <c r="O6" t="n">
-        <v>7.278911908769627</v>
+        <v>7.265389072117189</v>
       </c>
       <c r="P6" t="n">
-        <v>281.9892217702392</v>
+        <v>281.9837051506128</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25755,28 +25847,28 @@
         <v>0.036</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4573199690807252</v>
+        <v>-0.4576680708186088</v>
       </c>
       <c r="J7" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K7" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1610795045018441</v>
+        <v>0.1624231707642221</v>
       </c>
       <c r="M7" t="n">
-        <v>5.938340629899182</v>
+        <v>5.91771747248956</v>
       </c>
       <c r="N7" t="n">
-        <v>57.03195833567677</v>
+        <v>56.8191791276677</v>
       </c>
       <c r="O7" t="n">
-        <v>7.551950631173165</v>
+        <v>7.537849768181089</v>
       </c>
       <c r="P7" t="n">
-        <v>283.6498317689997</v>
+        <v>283.653506337584</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25833,28 +25925,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4916262161029415</v>
+        <v>-0.4881208632743564</v>
       </c>
       <c r="J8" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K8" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1502981705592653</v>
+        <v>0.1494116370375617</v>
       </c>
       <c r="M8" t="n">
-        <v>6.529293522995654</v>
+        <v>6.519435752432864</v>
       </c>
       <c r="N8" t="n">
-        <v>71.0703063612328</v>
+        <v>70.87991685616466</v>
       </c>
       <c r="O8" t="n">
-        <v>8.430320655896358</v>
+        <v>8.419021134084689</v>
       </c>
       <c r="P8" t="n">
-        <v>289.3916568955754</v>
+        <v>289.3544847216631</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25911,28 +26003,28 @@
         <v>0.0421</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4368473020999557</v>
+        <v>-0.4320404402408507</v>
       </c>
       <c r="J9" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K9" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09664038523062191</v>
+        <v>0.09544797148850481</v>
       </c>
       <c r="M9" t="n">
-        <v>7.608975846955042</v>
+        <v>7.586378162919784</v>
       </c>
       <c r="N9" t="n">
-        <v>92.78261227395276</v>
+        <v>92.43769218716126</v>
       </c>
       <c r="O9" t="n">
-        <v>9.632373138222624</v>
+        <v>9.614452256221426</v>
       </c>
       <c r="P9" t="n">
-        <v>303.8096895140295</v>
+        <v>303.7588122123246</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25970,7 +26062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J533"/>
+  <dimension ref="A1:J535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53656,10 +53748,114 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>-46.498523580457906,169.70922804780622</t>
+          <t>-46.49852742540063,169.70928337155098</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-46.4942030829052,169.7096382425593</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-46.49480877312756,169.7094135348415</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-46.49542309123355,169.7093130682222</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-46.49603645680638,169.70919899722287</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-46.49665890997622,169.7092157800489</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-46.497275971449845,169.7091550873388</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-46.49790141826722,169.70921514676692</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>-46.4985322247883,169.70935242907208</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:15:17+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-46.494204676617386,169.70966117355132</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-46.4948097095741,169.7094270085629</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-46.4954235504591,169.70931967560108</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-46.49603695205732,169.70920612290627</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-46.496658693866735,169.70921267062425</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-46.49727621457505,169.7091585854808</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>-46.49790203958313,169.70922408656665</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>-46.49853258496582,169.70935761162585</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0542/nzd0542.xlsx
+++ b/data/nzd0542/nzd0542.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J535"/>
+  <dimension ref="A1:J537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19690,6 +19690,78 @@
         <v>296.64</v>
       </c>
       <c r="J535" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>296.02</v>
+      </c>
+      <c r="C536" t="n">
+        <v>279.88</v>
+      </c>
+      <c r="D536" t="n">
+        <v>275.07</v>
+      </c>
+      <c r="E536" t="n">
+        <v>271.25</v>
+      </c>
+      <c r="F536" t="n">
+        <v>275.45</v>
+      </c>
+      <c r="G536" t="n">
+        <v>276.92</v>
+      </c>
+      <c r="H536" t="n">
+        <v>291.14</v>
+      </c>
+      <c r="I536" t="n">
+        <v>305.96</v>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>295.13</v>
+      </c>
+      <c r="C537" t="n">
+        <v>279.23</v>
+      </c>
+      <c r="D537" t="n">
+        <v>273.7</v>
+      </c>
+      <c r="E537" t="n">
+        <v>271.28</v>
+      </c>
+      <c r="F537" t="n">
+        <v>274.14</v>
+      </c>
+      <c r="G537" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="H537" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="I537" t="n">
+        <v>302.6</v>
+      </c>
+      <c r="J537" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19706,7 +19778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B558"/>
+  <dimension ref="A1:B560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25289,6 +25361,26 @@
       </c>
       <c r="B558" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -25457,28 +25549,28 @@
         <v>0.0309</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.348556794867436</v>
+        <v>-0.3481199305912483</v>
       </c>
       <c r="J2" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K2" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03707641095883074</v>
+        <v>0.03729238314047312</v>
       </c>
       <c r="M2" t="n">
-        <v>10.0905208739015</v>
+        <v>10.05489386237271</v>
       </c>
       <c r="N2" t="n">
-        <v>164.8825482838907</v>
+        <v>164.268068242288</v>
       </c>
       <c r="O2" t="n">
-        <v>12.84065996294157</v>
+        <v>12.81671050785996</v>
       </c>
       <c r="P2" t="n">
-        <v>304.2135419393366</v>
+        <v>304.208878958797</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25535,28 +25627,28 @@
         <v>0.0262</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4016314652907365</v>
+        <v>-0.4049130679190527</v>
       </c>
       <c r="J3" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K3" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06342663695689954</v>
+        <v>0.06488445213761695</v>
       </c>
       <c r="M3" t="n">
-        <v>8.660121871408121</v>
+        <v>8.642600895270901</v>
       </c>
       <c r="N3" t="n">
-        <v>124.879687358739</v>
+        <v>124.4776031038332</v>
       </c>
       <c r="O3" t="n">
-        <v>11.17495804729213</v>
+        <v>11.15695312815435</v>
       </c>
       <c r="P3" t="n">
-        <v>294.3819822107868</v>
+        <v>294.4169887760855</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25613,28 +25705,28 @@
         <v>0.0305</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3870617495774789</v>
+        <v>-0.3899834565159634</v>
       </c>
       <c r="J4" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K4" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09442400099772408</v>
+        <v>0.0963954147561894</v>
       </c>
       <c r="M4" t="n">
-        <v>6.77865936419533</v>
+        <v>6.767381764018157</v>
       </c>
       <c r="N4" t="n">
-        <v>75.58229429331739</v>
+        <v>75.35467978743127</v>
       </c>
       <c r="O4" t="n">
-        <v>8.693807813226456</v>
+        <v>8.680707332206936</v>
       </c>
       <c r="P4" t="n">
-        <v>288.3877177281695</v>
+        <v>288.4187765520086</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25691,28 +25783,28 @@
         <v>0.0369</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4083951415506673</v>
+        <v>-0.4078947981068941</v>
       </c>
       <c r="J5" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K5" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1260665315194118</v>
+        <v>0.1267343170532027</v>
       </c>
       <c r="M5" t="n">
-        <v>6.306069821373166</v>
+        <v>6.285050894137219</v>
       </c>
       <c r="N5" t="n">
-        <v>60.82144812226591</v>
+        <v>60.59604913832413</v>
       </c>
       <c r="O5" t="n">
-        <v>7.798810686397376</v>
+        <v>7.784346416901301</v>
       </c>
       <c r="P5" t="n">
-        <v>281.3992303972591</v>
+        <v>281.3939119290864</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25769,28 +25861,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4576358245418586</v>
+        <v>-0.4538560724339082</v>
       </c>
       <c r="J6" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K6" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1726703996409675</v>
+        <v>0.1712793967007123</v>
       </c>
       <c r="M6" t="n">
-        <v>5.792518374648097</v>
+        <v>5.78718904621952</v>
       </c>
       <c r="N6" t="n">
-        <v>52.78587836923987</v>
+        <v>52.67870900964659</v>
       </c>
       <c r="O6" t="n">
-        <v>7.265389072117189</v>
+        <v>7.258009989635354</v>
       </c>
       <c r="P6" t="n">
-        <v>281.9837051506128</v>
+        <v>281.943530693009</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25847,28 +25939,28 @@
         <v>0.036</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4576680708186088</v>
+        <v>-0.4529509422051354</v>
       </c>
       <c r="J7" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K7" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1624231707642221</v>
+        <v>0.1604390160388682</v>
       </c>
       <c r="M7" t="n">
-        <v>5.91771747248956</v>
+        <v>5.91918771889906</v>
       </c>
       <c r="N7" t="n">
-        <v>56.8191791276677</v>
+        <v>56.74667286634539</v>
       </c>
       <c r="O7" t="n">
-        <v>7.537849768181089</v>
+        <v>7.533038753806156</v>
       </c>
       <c r="P7" t="n">
-        <v>283.653506337584</v>
+        <v>283.6033627745563</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25925,28 +26017,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4881208632743564</v>
+        <v>-0.4781328874114449</v>
       </c>
       <c r="J8" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K8" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1494116370375617</v>
+        <v>0.1442050447357152</v>
       </c>
       <c r="M8" t="n">
-        <v>6.519435752432864</v>
+        <v>6.537577825069831</v>
       </c>
       <c r="N8" t="n">
-        <v>70.87991685616466</v>
+        <v>71.23732532331998</v>
       </c>
       <c r="O8" t="n">
-        <v>8.419021134084689</v>
+        <v>8.440220691624122</v>
       </c>
       <c r="P8" t="n">
-        <v>289.3544847216631</v>
+        <v>289.2478443550928</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26003,28 +26095,28 @@
         <v>0.0421</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4320404402408507</v>
+        <v>-0.4227677926724598</v>
       </c>
       <c r="J9" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K9" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09544797148850481</v>
+        <v>0.09199589254235396</v>
       </c>
       <c r="M9" t="n">
-        <v>7.586378162919784</v>
+        <v>7.599835779436728</v>
       </c>
       <c r="N9" t="n">
-        <v>92.43769218716126</v>
+        <v>92.62842245998827</v>
       </c>
       <c r="O9" t="n">
-        <v>9.614452256221426</v>
+        <v>9.624366080942073</v>
       </c>
       <c r="P9" t="n">
-        <v>303.7588122123246</v>
+        <v>303.6598092771144</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26062,7 +26154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J535"/>
+  <dimension ref="A1:J537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53861,6 +53953,110 @@
         </is>
       </c>
     </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-46.49421437385234,169.7098007028422</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-46.49481666984373,169.7095271546054</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-46.495429160183704,169.7094003892792</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-46.49604253485551,169.70928644880252</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>-46.49666312409399,169.70927641383548</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-46.497281248143516,169.70923100998422</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-46.49791084598629,169.70935079853655</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>-46.498540977035844,169.70947836515143</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-46.49421357250879,169.70978917256429</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-46.49481608457214,169.70951873352692</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-46.4954279265894,169.7093826400417</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-46.49604256186892,169.70928683747624</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-46.49666194450441,169.70925944155647</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-46.4972826078295,169.7092505736721</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>-46.4979075683638,169.70930363783862</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>-46.49853795158317,169.70943483168645</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0542/nzd0542.xlsx
+++ b/data/nzd0542/nzd0542.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J537"/>
+  <dimension ref="A1:J539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19764,6 +19764,78 @@
       <c r="J537" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>293.58</v>
+      </c>
+      <c r="C538" t="n">
+        <v>277.67</v>
+      </c>
+      <c r="D538" t="n">
+        <v>272.01</v>
+      </c>
+      <c r="E538" t="n">
+        <v>269.28</v>
+      </c>
+      <c r="F538" t="n">
+        <v>271.52</v>
+      </c>
+      <c r="G538" t="n">
+        <v>275.77</v>
+      </c>
+      <c r="H538" t="n">
+        <v>285.97</v>
+      </c>
+      <c r="I538" t="n">
+        <v>303.18</v>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>292.73</v>
+      </c>
+      <c r="C539" t="n">
+        <v>276.68</v>
+      </c>
+      <c r="D539" t="n">
+        <v>270.98</v>
+      </c>
+      <c r="E539" t="n">
+        <v>268.68</v>
+      </c>
+      <c r="F539" t="n">
+        <v>270.87</v>
+      </c>
+      <c r="G539" t="n">
+        <v>275.04</v>
+      </c>
+      <c r="H539" t="n">
+        <v>284.73</v>
+      </c>
+      <c r="I539" t="n">
+        <v>303.23</v>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B560"/>
+  <dimension ref="A1:B562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25381,6 +25453,26 @@
       </c>
       <c r="B560" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -25549,28 +25641,28 @@
         <v>0.0309</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3481199305912483</v>
+        <v>-0.3495403222663205</v>
       </c>
       <c r="J2" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K2" t="n">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03729238314047312</v>
+        <v>0.03789283408671407</v>
       </c>
       <c r="M2" t="n">
-        <v>10.05489386237271</v>
+        <v>10.02422487015559</v>
       </c>
       <c r="N2" t="n">
-        <v>164.268068242288</v>
+        <v>163.6693411941323</v>
       </c>
       <c r="O2" t="n">
-        <v>12.81671050785996</v>
+        <v>12.79333190353992</v>
       </c>
       <c r="P2" t="n">
-        <v>304.208878958797</v>
+        <v>304.224095014012</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25627,28 +25719,28 @@
         <v>0.0262</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4049130679190527</v>
+        <v>-0.4099536088051238</v>
       </c>
       <c r="J3" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K3" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06488445213761695</v>
+        <v>0.06685278563976105</v>
       </c>
       <c r="M3" t="n">
-        <v>8.642600895270901</v>
+        <v>8.633302099244233</v>
       </c>
       <c r="N3" t="n">
-        <v>124.4776031038332</v>
+        <v>124.1702436093824</v>
       </c>
       <c r="O3" t="n">
-        <v>11.15695312815435</v>
+        <v>11.14317026745003</v>
       </c>
       <c r="P3" t="n">
-        <v>294.4169887760855</v>
+        <v>294.4709273290682</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25705,28 +25797,28 @@
         <v>0.0305</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3899834565159634</v>
+        <v>-0.3950527584178786</v>
       </c>
       <c r="J4" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K4" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0963954147561894</v>
+        <v>0.0992365875814093</v>
       </c>
       <c r="M4" t="n">
-        <v>6.767381764018157</v>
+        <v>6.766745194036078</v>
       </c>
       <c r="N4" t="n">
-        <v>75.35467978743127</v>
+        <v>75.2352468870809</v>
       </c>
       <c r="O4" t="n">
-        <v>8.680707332206936</v>
+        <v>8.673825389473834</v>
       </c>
       <c r="P4" t="n">
-        <v>288.4187765520086</v>
+        <v>288.4728314874475</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25783,28 +25875,28 @@
         <v>0.0369</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4078947981068941</v>
+        <v>-0.4091361093038741</v>
       </c>
       <c r="J5" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K5" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1267343170532027</v>
+        <v>0.1283387005359616</v>
       </c>
       <c r="M5" t="n">
-        <v>6.285050894137219</v>
+        <v>6.267378933286166</v>
       </c>
       <c r="N5" t="n">
-        <v>60.59604913832413</v>
+        <v>60.38067813382426</v>
       </c>
       <c r="O5" t="n">
-        <v>7.784346416901301</v>
+        <v>7.770500507291938</v>
       </c>
       <c r="P5" t="n">
-        <v>281.3939119290864</v>
+        <v>281.4071494383866</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25861,28 +25953,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4538560724339082</v>
+        <v>-0.4528816802865004</v>
       </c>
       <c r="J6" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K6" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1712793967007123</v>
+        <v>0.1718603663409252</v>
       </c>
       <c r="M6" t="n">
-        <v>5.78718904621952</v>
+        <v>5.769887317221642</v>
       </c>
       <c r="N6" t="n">
-        <v>52.67870900964659</v>
+        <v>52.48915494146255</v>
       </c>
       <c r="O6" t="n">
-        <v>7.258009989635354</v>
+        <v>7.244939954303455</v>
       </c>
       <c r="P6" t="n">
-        <v>281.943530693009</v>
+        <v>281.9331434334093</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25939,28 +26031,28 @@
         <v>0.036</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4529509422051354</v>
+        <v>-0.4500346235364467</v>
       </c>
       <c r="J7" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K7" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1604390160388682</v>
+        <v>0.1597187746049497</v>
       </c>
       <c r="M7" t="n">
-        <v>5.91918771889906</v>
+        <v>5.911892063754443</v>
       </c>
       <c r="N7" t="n">
-        <v>56.74667286634539</v>
+        <v>56.58909956067728</v>
       </c>
       <c r="O7" t="n">
-        <v>7.533038753806156</v>
+        <v>7.522572669019375</v>
       </c>
       <c r="P7" t="n">
-        <v>283.6033627745563</v>
+        <v>283.572270050136</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26017,28 +26109,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4781328874114449</v>
+        <v>-0.4713578810875406</v>
       </c>
       <c r="J8" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K8" t="n">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1442050447357152</v>
+        <v>0.141267968178147</v>
       </c>
       <c r="M8" t="n">
-        <v>6.537577825069831</v>
+        <v>6.542300530557196</v>
       </c>
       <c r="N8" t="n">
-        <v>71.23732532331998</v>
+        <v>71.25607861582795</v>
       </c>
       <c r="O8" t="n">
-        <v>8.440220691624122</v>
+        <v>8.441331566514133</v>
       </c>
       <c r="P8" t="n">
-        <v>289.2478443550928</v>
+        <v>289.1752848875034</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26095,28 +26187,28 @@
         <v>0.0421</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4227677926724598</v>
+        <v>-0.4144652438771525</v>
       </c>
       <c r="J9" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K9" t="n">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09199589254235396</v>
+        <v>0.08905500595208093</v>
       </c>
       <c r="M9" t="n">
-        <v>7.599835779436728</v>
+        <v>7.60933459431264</v>
       </c>
       <c r="N9" t="n">
-        <v>92.62842245998827</v>
+        <v>92.70783947860869</v>
       </c>
       <c r="O9" t="n">
-        <v>9.624366080942073</v>
+        <v>9.628491028121109</v>
       </c>
       <c r="P9" t="n">
-        <v>303.6598092771144</v>
+        <v>303.5708845367653</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26154,7 +26246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J537"/>
+  <dimension ref="A1:J539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54057,6 +54149,110 @@
         </is>
       </c>
     </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-46.49421217690771,169.7097690917442</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>-46.49481467991785,169.70949852293944</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>-46.49542640485252,169.70936074499824</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-46.496040760972484,169.70926092589463</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>-46.49665958531775,169.7092254970011</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-46.49728021261885,169.70921611048757</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-46.497906190676034,169.7092838148</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-46.4985384738351,169.7094423463913</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-46.49421141157661,169.7097580796821</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>-46.494813788500764,169.70948569699036</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>-46.495425477401376,169.7093474006825</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-46.49604022070241,169.70925315242056</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>-46.49665900002181,169.7092170756425</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-46.497279555284805,169.70920665254658</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-46.49790507411613,169.70926774907022</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>-46.4985385188568,169.70944299421072</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0542/nzd0542.xlsx
+++ b/data/nzd0542/nzd0542.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J539"/>
+  <dimension ref="A1:J544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19836,6 +19836,186 @@
       <c r="J539" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>293.04</v>
+      </c>
+      <c r="C540" t="n">
+        <v>278.11</v>
+      </c>
+      <c r="D540" t="n">
+        <v>272.34</v>
+      </c>
+      <c r="E540" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="F540" t="n">
+        <v>272.39</v>
+      </c>
+      <c r="G540" t="n">
+        <v>276.52</v>
+      </c>
+      <c r="H540" t="n">
+        <v>286.21</v>
+      </c>
+      <c r="I540" t="n">
+        <v>303.69</v>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>292.67</v>
+      </c>
+      <c r="C541" t="n">
+        <v>279.19</v>
+      </c>
+      <c r="D541" t="n">
+        <v>273.11</v>
+      </c>
+      <c r="E541" t="n">
+        <v>270.61</v>
+      </c>
+      <c r="F541" t="n">
+        <v>272.57</v>
+      </c>
+      <c r="G541" t="n">
+        <v>276.53</v>
+      </c>
+      <c r="H541" t="n">
+        <v>285.95</v>
+      </c>
+      <c r="I541" t="n">
+        <v>302.46</v>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>292.75</v>
+      </c>
+      <c r="C542" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="D542" t="n">
+        <v>274.76</v>
+      </c>
+      <c r="E542" t="n">
+        <v>272.23</v>
+      </c>
+      <c r="F542" t="n">
+        <v>273.86</v>
+      </c>
+      <c r="G542" t="n">
+        <v>277.64</v>
+      </c>
+      <c r="H542" t="n">
+        <v>286.57</v>
+      </c>
+      <c r="I542" t="n">
+        <v>302.47</v>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>294.65</v>
+      </c>
+      <c r="C543" t="n">
+        <v>281.85</v>
+      </c>
+      <c r="D543" t="n">
+        <v>276.79</v>
+      </c>
+      <c r="E543" t="n">
+        <v>274.1</v>
+      </c>
+      <c r="F543" t="n">
+        <v>275.64</v>
+      </c>
+      <c r="G543" t="n">
+        <v>279.24</v>
+      </c>
+      <c r="H543" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="I543" t="n">
+        <v>302.88</v>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>298.16</v>
+      </c>
+      <c r="C544" t="n">
+        <v>285.7</v>
+      </c>
+      <c r="D544" t="n">
+        <v>279.48</v>
+      </c>
+      <c r="E544" t="n">
+        <v>276.04</v>
+      </c>
+      <c r="F544" t="n">
+        <v>277.29</v>
+      </c>
+      <c r="G544" t="n">
+        <v>280.79</v>
+      </c>
+      <c r="H544" t="n">
+        <v>287.96</v>
+      </c>
+      <c r="I544" t="n">
+        <v>305.23</v>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19850,7 +20030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B562"/>
+  <dimension ref="A1:B567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25473,6 +25653,56 @@
       </c>
       <c r="B562" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -25641,28 +25871,28 @@
         <v>0.0309</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3495403222663205</v>
+        <v>-0.350830895070906</v>
       </c>
       <c r="J2" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K2" t="n">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03789283408671407</v>
+        <v>0.03893235230226921</v>
       </c>
       <c r="M2" t="n">
-        <v>10.02422487015559</v>
+        <v>9.949843315505271</v>
       </c>
       <c r="N2" t="n">
-        <v>163.6693411941323</v>
+        <v>162.2039974227278</v>
       </c>
       <c r="O2" t="n">
-        <v>12.79333190353992</v>
+        <v>12.73593331573025</v>
       </c>
       <c r="P2" t="n">
-        <v>304.224095014012</v>
+        <v>304.2379252134925</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25719,28 +25949,28 @@
         <v>0.0262</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4099536088051238</v>
+        <v>-0.4149571183727972</v>
       </c>
       <c r="J3" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K3" t="n">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06685278563976105</v>
+        <v>0.06966506347051682</v>
       </c>
       <c r="M3" t="n">
-        <v>8.633302099244233</v>
+        <v>8.584136181715126</v>
       </c>
       <c r="N3" t="n">
-        <v>124.1702436093824</v>
+        <v>123.1508542154439</v>
       </c>
       <c r="O3" t="n">
-        <v>11.14317026745003</v>
+        <v>11.09733545565979</v>
       </c>
       <c r="P3" t="n">
-        <v>294.4709273290682</v>
+        <v>294.5245866383702</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25797,28 +26027,28 @@
         <v>0.0305</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3950527584178786</v>
+        <v>-0.4000830963069838</v>
       </c>
       <c r="J4" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K4" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0992365875814093</v>
+        <v>0.1032941275204521</v>
       </c>
       <c r="M4" t="n">
-        <v>6.766745194036078</v>
+        <v>6.734298855431033</v>
       </c>
       <c r="N4" t="n">
-        <v>75.2352468870809</v>
+        <v>74.66921783518065</v>
       </c>
       <c r="O4" t="n">
-        <v>8.673825389473834</v>
+        <v>8.641135216809227</v>
       </c>
       <c r="P4" t="n">
-        <v>288.4728314874475</v>
+        <v>288.5265882614885</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25875,28 +26105,28 @@
         <v>0.0369</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4091361093038741</v>
+        <v>-0.405243655450455</v>
       </c>
       <c r="J5" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K5" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1283387005359616</v>
+        <v>0.1283905194494129</v>
       </c>
       <c r="M5" t="n">
-        <v>6.267378933286166</v>
+        <v>6.231167997163181</v>
       </c>
       <c r="N5" t="n">
-        <v>60.38067813382426</v>
+        <v>59.90847333718583</v>
       </c>
       <c r="O5" t="n">
-        <v>7.770500507291938</v>
+        <v>7.740056416925256</v>
       </c>
       <c r="P5" t="n">
-        <v>281.4071494383866</v>
+        <v>281.3654654763827</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25953,28 +26183,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4528816802865004</v>
+        <v>-0.4445305564628038</v>
       </c>
       <c r="J6" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K6" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1718603663409252</v>
+        <v>0.1689964975942921</v>
       </c>
       <c r="M6" t="n">
-        <v>5.769887317221642</v>
+        <v>5.752784213243713</v>
       </c>
       <c r="N6" t="n">
-        <v>52.48915494146255</v>
+        <v>52.21499047094156</v>
       </c>
       <c r="O6" t="n">
-        <v>7.244939954303455</v>
+        <v>7.225994081850715</v>
       </c>
       <c r="P6" t="n">
-        <v>281.9331434334093</v>
+        <v>281.8437717473997</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26031,28 +26261,28 @@
         <v>0.036</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4500346235364467</v>
+        <v>-0.4377782966686274</v>
       </c>
       <c r="J7" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K7" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1597187746049497</v>
+        <v>0.1542334101908711</v>
       </c>
       <c r="M7" t="n">
-        <v>5.911892063754443</v>
+        <v>5.919905715261144</v>
       </c>
       <c r="N7" t="n">
-        <v>56.58909956067728</v>
+        <v>56.47384180916684</v>
       </c>
       <c r="O7" t="n">
-        <v>7.522572669019375</v>
+        <v>7.51490797077162</v>
       </c>
       <c r="P7" t="n">
-        <v>283.572270050136</v>
+        <v>283.441128854026</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26109,28 +26339,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4713578810875406</v>
+        <v>-0.4522212455264081</v>
       </c>
       <c r="J8" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K8" t="n">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="L8" t="n">
-        <v>0.141267968178147</v>
+        <v>0.1324297482810408</v>
       </c>
       <c r="M8" t="n">
-        <v>6.542300530557196</v>
+        <v>6.564819831033382</v>
       </c>
       <c r="N8" t="n">
-        <v>71.25607861582795</v>
+        <v>71.52265026954775</v>
       </c>
       <c r="O8" t="n">
-        <v>8.441331566514133</v>
+        <v>8.457106495105034</v>
       </c>
       <c r="P8" t="n">
-        <v>289.1752848875034</v>
+        <v>288.9696457030852</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26187,28 +26417,28 @@
         <v>0.0421</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4144652438771525</v>
+        <v>-0.3941029831848019</v>
       </c>
       <c r="J9" t="n">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="K9" t="n">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08905500595208093</v>
+        <v>0.08193770465092465</v>
       </c>
       <c r="M9" t="n">
-        <v>7.60933459431264</v>
+        <v>7.633691911304763</v>
       </c>
       <c r="N9" t="n">
-        <v>92.70783947860869</v>
+        <v>92.90313704815419</v>
       </c>
       <c r="O9" t="n">
-        <v>9.628491028121109</v>
+        <v>9.63862734252934</v>
       </c>
       <c r="P9" t="n">
-        <v>303.5708845367653</v>
+        <v>303.352080605794</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26246,7 +26476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J539"/>
+  <dimension ref="A1:J544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54253,6 +54483,266 @@
         </is>
       </c>
     </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>-46.49421169069748,169.70976209584586</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>-46.494815076102746,169.70950422336142</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>-46.49542670199674,169.70936502036164</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-46.49604147232727,169.7092711609691</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-46.49666036871291,169.70923676866605</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-46.49728088796124,169.7092258275505</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-46.49790640678414,169.70928692429618</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-46.49853893305622,169.70944895414917</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>-46.49421135755319,169.7097573023601</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>-46.494816048555414,169.7095182153067</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>-46.49542739533263,169.7093749962098</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-46.496041958569265,169.70927815709618</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-46.49666053079453,169.70923910073472</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-46.4972808969658,169.70922595711136</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-46.49790617266702,169.7092835556753</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-46.49853782552227,169.70943301779224</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-46.494211429584404,169.70975833878944</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>-46.494816588806174,169.7095259886099</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>-46.495428881049456,169.70939637302828</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-46.496043417292675,169.70929914547818</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-46.496661692378076,169.70925581389392</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>-46.49728189647102,169.70924033836505</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>-46.49790673094615,169.70929158854048</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>-46.498537834526616,169.7094331473561</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-46.49421314032302,169.7097829539876</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-46.494818443663064,169.70955267695228</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-46.49543070892595,169.70942267299478</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-46.49604510112295,169.7093233728097</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-46.49666329517931,169.7092788754638</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-46.497283337196116,169.7092610681012</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-46.49790735225613,169.70930052834228</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-46.49853820370484,169.709438459475</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-46.49421630067367,169.70982842733224</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-46.49482191024795,169.70960255565615</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-46.49543313107813,169.70945752369246</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-46.49604684797894,169.7093485070486</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-46.49666478091789,169.70930025276317</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-46.497284732894975,169.70928115003434</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-46.497907982569906,169.70930959770664</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>-46.49854031972164,169.7094689069874</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0542/nzd0542.xlsx
+++ b/data/nzd0542/nzd0542.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J544"/>
+  <dimension ref="A1:J548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20014,6 +20014,150 @@
         <v>305.23</v>
       </c>
       <c r="J544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>296.29</v>
+      </c>
+      <c r="C545" t="n">
+        <v>284.48</v>
+      </c>
+      <c r="D545" t="n">
+        <v>279.34</v>
+      </c>
+      <c r="E545" t="n">
+        <v>273.26</v>
+      </c>
+      <c r="F545" t="n">
+        <v>280.86</v>
+      </c>
+      <c r="G545" t="n">
+        <v>283.21</v>
+      </c>
+      <c r="H545" t="n">
+        <v>290.6</v>
+      </c>
+      <c r="I545" t="n">
+        <v>303.51</v>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>296.29</v>
+      </c>
+      <c r="C546" t="n">
+        <v>284.48</v>
+      </c>
+      <c r="D546" t="n">
+        <v>279.34</v>
+      </c>
+      <c r="E546" t="n">
+        <v>270.31</v>
+      </c>
+      <c r="F546" t="n">
+        <v>280.86</v>
+      </c>
+      <c r="G546" t="n">
+        <v>283.21</v>
+      </c>
+      <c r="H546" t="n">
+        <v>290.6</v>
+      </c>
+      <c r="I546" t="n">
+        <v>303.51</v>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>298.74</v>
+      </c>
+      <c r="C547" t="n">
+        <v>287.27</v>
+      </c>
+      <c r="D547" t="n">
+        <v>281.03</v>
+      </c>
+      <c r="E547" t="n">
+        <v>266.65</v>
+      </c>
+      <c r="F547" t="n">
+        <v>280.86</v>
+      </c>
+      <c r="G547" t="n">
+        <v>283.21</v>
+      </c>
+      <c r="H547" t="n">
+        <v>290.6</v>
+      </c>
+      <c r="I547" t="n">
+        <v>303.51</v>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>298.74</v>
+      </c>
+      <c r="C548" t="n">
+        <v>287.27</v>
+      </c>
+      <c r="D548" t="n">
+        <v>281.03</v>
+      </c>
+      <c r="E548" t="n">
+        <v>266.65</v>
+      </c>
+      <c r="F548" t="n">
+        <v>285.59</v>
+      </c>
+      <c r="G548" t="n">
+        <v>292.3</v>
+      </c>
+      <c r="H548" t="n">
+        <v>306.75</v>
+      </c>
+      <c r="I548" t="n">
+        <v>323.13</v>
+      </c>
+      <c r="J548" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20030,7 +20174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25703,6 +25847,46 @@
       </c>
       <c r="B567" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -25871,28 +26055,28 @@
         <v>0.0309</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.350830895070906</v>
+        <v>-0.3468992249926696</v>
       </c>
       <c r="J2" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="K2" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03893235230226921</v>
+        <v>0.03869677295613105</v>
       </c>
       <c r="M2" t="n">
-        <v>9.949843315505271</v>
+        <v>9.896340735636855</v>
       </c>
       <c r="N2" t="n">
-        <v>162.2039974227278</v>
+        <v>161.0764957162359</v>
       </c>
       <c r="O2" t="n">
-        <v>12.73593331573025</v>
+        <v>12.69159153598302</v>
       </c>
       <c r="P2" t="n">
-        <v>304.2379252134925</v>
+        <v>304.195465550554</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25949,28 +26133,28 @@
         <v>0.0262</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4149571183727972</v>
+        <v>-0.4113493505138829</v>
       </c>
       <c r="J3" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="K3" t="n">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06966506347051682</v>
+        <v>0.06957791867552732</v>
       </c>
       <c r="M3" t="n">
-        <v>8.584136181715126</v>
+        <v>8.539618284114082</v>
       </c>
       <c r="N3" t="n">
-        <v>123.1508542154439</v>
+        <v>122.3018033067224</v>
       </c>
       <c r="O3" t="n">
-        <v>11.09733545565979</v>
+        <v>11.05901457213627</v>
       </c>
       <c r="P3" t="n">
-        <v>294.5245866383702</v>
+        <v>294.4856581136584</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26027,28 +26211,28 @@
         <v>0.0305</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4000830963069838</v>
+        <v>-0.3966278352263202</v>
       </c>
       <c r="J4" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="K4" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1032941275204521</v>
+        <v>0.1031654383570867</v>
       </c>
       <c r="M4" t="n">
-        <v>6.734298855431033</v>
+        <v>6.702006491498765</v>
       </c>
       <c r="N4" t="n">
-        <v>74.66921783518065</v>
+        <v>74.16718382264622</v>
       </c>
       <c r="O4" t="n">
-        <v>8.641135216809227</v>
+        <v>8.6120371470777</v>
       </c>
       <c r="P4" t="n">
-        <v>288.5265882614885</v>
+        <v>288.4894408875891</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26105,28 +26289,28 @@
         <v>0.0369</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.405243655450455</v>
+        <v>-0.4072285111540739</v>
       </c>
       <c r="J5" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="K5" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1283905194494129</v>
+        <v>0.1312335606165519</v>
       </c>
       <c r="M5" t="n">
-        <v>6.231167997163181</v>
+        <v>6.20473943594147</v>
       </c>
       <c r="N5" t="n">
-        <v>59.90847333718583</v>
+        <v>59.53903310237553</v>
       </c>
       <c r="O5" t="n">
-        <v>7.740056416925256</v>
+        <v>7.716154035682253</v>
       </c>
       <c r="P5" t="n">
-        <v>281.3654654763827</v>
+        <v>281.3868259849868</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26183,28 +26367,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4445305564628038</v>
+        <v>-0.4266536912099618</v>
       </c>
       <c r="J6" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="K6" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1689964975942921</v>
+        <v>0.1572661194875892</v>
       </c>
       <c r="M6" t="n">
-        <v>5.752784213243713</v>
+        <v>5.787588461198336</v>
       </c>
       <c r="N6" t="n">
-        <v>52.21499047094156</v>
+        <v>52.90218368701065</v>
       </c>
       <c r="O6" t="n">
-        <v>7.225994081850715</v>
+        <v>7.273388734765292</v>
       </c>
       <c r="P6" t="n">
-        <v>281.8437717473997</v>
+        <v>281.6515955117083</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26261,28 +26445,28 @@
         <v>0.036</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4377782966686274</v>
+        <v>-0.41743216534571</v>
       </c>
       <c r="J7" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="K7" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1542334101908711</v>
+        <v>0.1411123539870038</v>
       </c>
       <c r="M7" t="n">
-        <v>5.919905715261144</v>
+        <v>5.982036477855276</v>
       </c>
       <c r="N7" t="n">
-        <v>56.47384180916684</v>
+        <v>57.51888276449925</v>
       </c>
       <c r="O7" t="n">
-        <v>7.51490797077162</v>
+        <v>7.584120434466956</v>
       </c>
       <c r="P7" t="n">
-        <v>283.441128854026</v>
+        <v>283.2223949556986</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26339,28 +26523,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4522212455264081</v>
+        <v>-0.4257720181876249</v>
       </c>
       <c r="J8" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="K8" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1324297482810408</v>
+        <v>0.1171545792765274</v>
       </c>
       <c r="M8" t="n">
-        <v>6.564819831033382</v>
+        <v>6.632667453617723</v>
       </c>
       <c r="N8" t="n">
-        <v>71.52265026954775</v>
+        <v>73.60706396777783</v>
       </c>
       <c r="O8" t="n">
-        <v>8.457106495105034</v>
+        <v>8.579455924927748</v>
       </c>
       <c r="P8" t="n">
-        <v>288.9696457030852</v>
+        <v>288.6840172595116</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26417,28 +26601,28 @@
         <v>0.0421</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3941029831848019</v>
+        <v>-0.3708733088435605</v>
       </c>
       <c r="J9" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="K9" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08193770465092465</v>
+        <v>0.07273226860026627</v>
       </c>
       <c r="M9" t="n">
-        <v>7.633691911304763</v>
+        <v>7.685984899312567</v>
       </c>
       <c r="N9" t="n">
-        <v>92.90313704815419</v>
+        <v>94.48634151499938</v>
       </c>
       <c r="O9" t="n">
-        <v>9.63862734252934</v>
+        <v>9.720408505561862</v>
       </c>
       <c r="P9" t="n">
-        <v>303.352080605794</v>
+        <v>303.1012012571493</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26476,7 +26660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J544"/>
+  <dimension ref="A1:J548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54743,6 +54927,214 @@
         </is>
       </c>
     </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-46.49421461695634,169.70980420079175</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-46.49482081174806,169.7095867499362</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-46.49543300501842,169.70945570990142</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-46.496044344750615,169.70931248994398</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-46.49666799550232,169.70934650547017</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-46.4972869119791,169.70931250376464</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>-46.49791035974681,169.70934380216883</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>-46.49853877097823,169.70944662199932</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-46.49421461695634,169.70980420079175</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-46.49482081174806,169.7095867499362</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-46.49543300501842,169.70945570990142</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-46.496041688434865,169.70927427035892</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-46.49666799550232,169.70934650547017</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-46.4972869119791,169.70931250376464</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>-46.49791035974681,169.70934380216883</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>-46.49853877097823,169.70944662199932</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-46.494216822895126,169.70983594144676</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-46.49482332388804,169.70962289580507</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-46.495434526737235,169.7094776049512</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-46.49603839278479,169.70922685216794</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-46.49666799550232,169.70934650547017</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-46.4972869119791,169.70931250376464</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>-46.49791035974681,169.70934380216883</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>-46.49853877097823,169.70944662199932</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-46.494216822895126,169.70983594144676</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-46.49482332388804,169.70962289580507</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-46.495434526737235,169.7094776049512</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-46.49603839278479,169.70922685216794</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-46.496672254572935,169.70940778707794</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-46.49729509697497,169.7094302746211</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>-46.497924901725135,169.70955304545203</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>-46.49855643720219,169.7097008264293</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
